--- a/public/template-import-karyawan.xlsx
+++ b/public/template-import-karyawan.xlsx
@@ -201,7 +201,7 @@
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>Teks bebas</t>
+        <t>Pilih dari daftar (sheet Referensi) atau ketik departemen baru — departemen baru otomatis terdaftar.</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
@@ -696,7 +696,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Operasional</t>
+          <t>Operation</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -7223,12 +7223,15 @@
       <c r="K501" s="7" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="H3:H501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"employee,hr,admin"</formula1>
     </dataValidation>
     <dataValidation sqref="I3:I501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Referensi!$A$3:$A$20</formula1>
+    </dataValidation>
+    <dataValidation sqref="D3:D501" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Departemen" prompt="Pilih dari daftar, atau ketik departemen baru." type="list">
+      <formula1>=Referensi!$H$2:$H$60</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7242,13 +7245,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7265,6 +7269,11 @@
       <c r="F1" s="8" t="inlineStr">
         <is>
           <t>Kode hari</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>Departemen</t>
         </is>
       </c>
     </row>
@@ -7289,6 +7298,11 @@
           <t>Sen</t>
         </is>
       </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>BOD</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
@@ -7311,6 +7325,11 @@
           <t>Sel</t>
         </is>
       </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Sales</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
@@ -7333,6 +7352,11 @@
           <t>Rab</t>
         </is>
       </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
@@ -7350,6 +7374,11 @@
           <t>Kam</t>
         </is>
       </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>HRGA</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="F6" s="10" t="inlineStr">
@@ -7357,6 +7386,11 @@
           <t>Jum</t>
         </is>
       </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="F7" s="10" t="inlineStr">
@@ -7364,6 +7398,11 @@
           <t>Sab</t>
         </is>
       </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="F8" s="10" t="inlineStr">
@@ -7371,6 +7410,60 @@
           <t>Min</t>
         </is>
       </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>Offline Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>Online Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>Operation</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>Reseller &amp; Whatsapp</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>Swarovski</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
